--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="165">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T12:31:04+00:00</t>
+    <t>2025-03-04T08:19:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,9 +449,6 @@
   </si>
   <si>
     <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to refer to a particular code in the system.</t>
@@ -1288,7 +1285,7 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>81</v>
@@ -1496,7 +1493,7 @@
         <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ6" t="s" s="2">
         <v>106</v>
@@ -1704,13 +1701,13 @@
         <v>78</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
@@ -1811,7 +1808,7 @@
         <v>78</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>106</v>
@@ -2019,13 +2016,13 @@
         <v>78</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -2126,7 +2123,7 @@
         <v>83</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>106</v>
@@ -2231,7 +2228,7 @@
         <v>83</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>106</v>
@@ -2276,11 +2273,9 @@
       <c r="M14" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="N14" t="s" s="2">
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>76</v>
@@ -2329,7 +2324,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -2338,21 +2333,21 @@
         <v>83</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2378,16 +2373,14 @@
         <v>84</v>
       </c>
       <c r="L15" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>146</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" s="2"/>
+      <c r="O15" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>76</v>
@@ -2436,7 +2429,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -2445,21 +2438,21 @@
         <v>83</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2482,19 +2475,19 @@
         <v>114</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="N16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>76</v>
@@ -2543,7 +2536,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -2552,21 +2545,21 @@
         <v>83</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2592,16 +2585,16 @@
         <v>84</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="O17" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>76</v>
@@ -2650,7 +2643,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -2659,13 +2652,13 @@
         <v>83</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:19:08+00:00</t>
+    <t>2025-03-27T13:15:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T13:15:18+00:00</t>
+    <t>2025-03-27T14:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T14:27:05+00:00</t>
+    <t>2025-03-27T15:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:41:15+00:00</t>
+    <t>2025-03-27T15:45:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:45:03+00:00</t>
+    <t>2025-03-27T15:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-27T15:47:29+00:00</t>
+    <t>2025-03-31T07:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:44:46+00:00</t>
+    <t>2025-03-31T07:48:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:14+00:00</t>
+    <t>2025-03-31T07:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T07:48:39+00:00</t>
+    <t>2025-03-31T11:47:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,8 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Moment de la mesure.
-Peut être exprimé par un texte libre ou un code.</t>
+    <t>Extension pour indiquer le moment de la mesure</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:47:14+00:00</t>
+    <t>2025-03-31T11:46:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T11:46:38+00:00</t>
+    <t>2025-03-31T14:05:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T14:05:37+00:00</t>
+    <t>2025-03-31T15:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:50:51+00:00</t>
+    <t>2025-03-31T15:55:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T15:55:12+00:00</t>
+    <t>2025-03-31T16:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:04:27+00:00</t>
+    <t>2025-03-31T16:16:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:16:40+00:00</t>
+    <t>2025-03-31T16:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:26:20+00:00</t>
+    <t>2025-03-31T16:37:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T16:37:23+00:00</t>
+    <t>2025-04-01T07:11:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:11:22+00:00</t>
+    <t>2025-04-01T07:12:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-01T07:12:21+00:00</t>
+    <t>2025-04-01T07:12:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:08+00:00</t>
+    <t>2025-07-07T09:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-07T09:50:30+00:00</t>
+    <t>2025-12-23T16:18:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T16:18:55+00:00</t>
+    <t>2026-01-06T09:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T09:57:05+00:00</t>
+    <t>2026-01-06T10:01:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-06T10:01:17+00:00</t>
+    <t>2026-01-19T08:51:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T08:51:58+00:00</t>
+    <t>2026-01-19T09:23:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:23:14+00:00</t>
+    <t>2026-01-19T09:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:39:10+00:00</t>
+    <t>2026-01-19T09:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:47:31+00:00</t>
+    <t>2026-01-19T09:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:54:18+00:00</t>
+    <t>2026-01-19T09:56:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T09:56:13+00:00</t>
+    <t>2026-01-19T10:07:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-19T10:07:50+00:00</t>
+    <t>2026-01-20T07:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T07:44:39+00:00</t>
+    <t>2026-01-20T09:11:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:11:57+00:00</t>
+    <t>2026-01-20T09:43:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:43:53+00:00</t>
+    <t>2026-01-20T09:47:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T09:47:48+00:00</t>
+    <t>2026-01-20T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:06:11+00:00</t>
+    <t>2026-01-20T11:11:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
+++ b/nr-add-lipids/ig/StructureDefinition-mesures-moment-of-measurement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T11:11:06+00:00</t>
+    <t>2026-01-20T12:50:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
